--- a/Overture-Match-Suggestions/KP.xlsx
+++ b/Overture-Match-Suggestions/KP.xlsx
@@ -2266,10 +2266,24 @@
           <t>Kangwŏn-doNorth Korea</t>
         </is>
       </c>
-      <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="n"/>
-      <c r="P21" s="2" t="n"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>KP-07</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>강원도</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="n"/>
       <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
@@ -2358,10 +2372,24 @@
           <t>Kangwŏn-doNorth Korea</t>
         </is>
       </c>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="2" t="n"/>
-      <c r="O22" s="2" t="n"/>
-      <c r="P22" s="2" t="n"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>KP-07</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>강원도</t>
+        </is>
+      </c>
       <c r="Q22" s="2" t="n"/>
       <c r="R22" s="2" t="n"/>
       <c r="S22" s="2" t="n"/>
@@ -3740,10 +3768,24 @@
           <t>Namp'oNorth Korea</t>
         </is>
       </c>
-      <c r="M38" s="2" t="n"/>
-      <c r="N38" s="2" t="n"/>
-      <c r="O38" s="2" t="n"/>
-      <c r="P38" s="2" t="n"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>KP-14</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>남포시</t>
+        </is>
+      </c>
       <c r="Q38" s="2" t="n"/>
       <c r="R38" s="2" t="n"/>
       <c r="S38" s="2" t="n"/>
@@ -3832,10 +3874,24 @@
           <t>Namp'oNorth Korea</t>
         </is>
       </c>
-      <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="n"/>
-      <c r="P39" s="2" t="n"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>KP-14</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>남포시</t>
+        </is>
+      </c>
       <c r="Q39" s="2" t="n"/>
       <c r="R39" s="2" t="n"/>
       <c r="S39" s="2" t="n"/>
@@ -3924,10 +3980,24 @@
           <t>Namp'oNorth Korea</t>
         </is>
       </c>
-      <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2" t="n"/>
-      <c r="O40" s="2" t="n"/>
-      <c r="P40" s="2" t="n"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>KP-14</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>남포시</t>
+        </is>
+      </c>
       <c r="Q40" s="2" t="n"/>
       <c r="R40" s="2" t="n"/>
       <c r="S40" s="2" t="n"/>
@@ -4016,10 +4086,24 @@
           <t>Namp'oNorth Korea</t>
         </is>
       </c>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2" t="n"/>
-      <c r="O41" s="2" t="n"/>
-      <c r="P41" s="2" t="n"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>KP-14</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>남포시</t>
+        </is>
+      </c>
       <c r="Q41" s="2" t="n"/>
       <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n"/>
@@ -4108,10 +4192,24 @@
           <t>Namp'oNorth Korea</t>
         </is>
       </c>
-      <c r="M42" s="2" t="n"/>
-      <c r="N42" s="2" t="n"/>
-      <c r="O42" s="2" t="n"/>
-      <c r="P42" s="2" t="n"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>KP-14</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>남포시</t>
+        </is>
+      </c>
       <c r="Q42" s="2" t="n"/>
       <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n"/>
@@ -4200,10 +4298,24 @@
           <t>Namp'oNorth Korea</t>
         </is>
       </c>
-      <c r="M43" s="2" t="n"/>
-      <c r="N43" s="2" t="n"/>
-      <c r="O43" s="2" t="n"/>
-      <c r="P43" s="2" t="n"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>KP-14</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>남포시</t>
+        </is>
+      </c>
       <c r="Q43" s="2" t="n"/>
       <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n"/>
@@ -9476,10 +9588,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M104" s="2" t="n"/>
-      <c r="N104" s="2" t="n"/>
-      <c r="O104" s="2" t="n"/>
-      <c r="P104" s="2" t="n"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q104" s="2" t="n"/>
       <c r="R104" s="2" t="n"/>
       <c r="S104" s="2" t="n"/>
@@ -9568,10 +9694,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M105" s="2" t="n"/>
-      <c r="N105" s="2" t="n"/>
-      <c r="O105" s="2" t="n"/>
-      <c r="P105" s="2" t="n"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q105" s="2" t="n"/>
       <c r="R105" s="2" t="n"/>
       <c r="S105" s="2" t="n"/>
@@ -9660,10 +9800,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M106" s="2" t="n"/>
-      <c r="N106" s="2" t="n"/>
-      <c r="O106" s="2" t="n"/>
-      <c r="P106" s="2" t="n"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q106" s="2" t="n"/>
       <c r="R106" s="2" t="n"/>
       <c r="S106" s="2" t="n"/>
@@ -9752,10 +9906,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M107" s="2" t="n"/>
-      <c r="N107" s="2" t="n"/>
-      <c r="O107" s="2" t="n"/>
-      <c r="P107" s="2" t="n"/>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q107" s="2" t="n"/>
       <c r="R107" s="2" t="n"/>
       <c r="S107" s="2" t="n"/>
@@ -9844,10 +10012,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M108" s="2" t="n"/>
-      <c r="N108" s="2" t="n"/>
-      <c r="O108" s="2" t="n"/>
-      <c r="P108" s="2" t="n"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q108" s="2" t="n"/>
       <c r="R108" s="2" t="n"/>
       <c r="S108" s="2" t="n"/>
@@ -9936,10 +10118,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M109" s="2" t="n"/>
-      <c r="N109" s="2" t="n"/>
-      <c r="O109" s="2" t="n"/>
-      <c r="P109" s="2" t="n"/>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q109" s="2" t="n"/>
       <c r="R109" s="2" t="n"/>
       <c r="S109" s="2" t="n"/>
@@ -10028,10 +10224,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M110" s="2" t="n"/>
-      <c r="N110" s="2" t="n"/>
-      <c r="O110" s="2" t="n"/>
-      <c r="P110" s="2" t="n"/>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q110" s="2" t="n"/>
       <c r="R110" s="2" t="n"/>
       <c r="S110" s="2" t="n"/>
@@ -10120,10 +10330,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M111" s="2" t="n"/>
-      <c r="N111" s="2" t="n"/>
-      <c r="O111" s="2" t="n"/>
-      <c r="P111" s="2" t="n"/>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q111" s="2" t="n"/>
       <c r="R111" s="2" t="n"/>
       <c r="S111" s="2" t="n"/>
@@ -10212,10 +10436,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M112" s="2" t="n"/>
-      <c r="N112" s="2" t="n"/>
-      <c r="O112" s="2" t="n"/>
-      <c r="P112" s="2" t="n"/>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q112" s="2" t="n"/>
       <c r="R112" s="2" t="n"/>
       <c r="S112" s="2" t="n"/>
@@ -10304,10 +10542,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M113" s="2" t="n"/>
-      <c r="N113" s="2" t="n"/>
-      <c r="O113" s="2" t="n"/>
-      <c r="P113" s="2" t="n"/>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q113" s="2" t="n"/>
       <c r="R113" s="2" t="n"/>
       <c r="S113" s="2" t="n"/>
@@ -10396,10 +10648,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M114" s="2" t="n"/>
-      <c r="N114" s="2" t="n"/>
-      <c r="O114" s="2" t="n"/>
-      <c r="P114" s="2" t="n"/>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q114" s="2" t="n"/>
       <c r="R114" s="2" t="n"/>
       <c r="S114" s="2" t="n"/>
@@ -10488,10 +10754,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M115" s="2" t="n"/>
-      <c r="N115" s="2" t="n"/>
-      <c r="O115" s="2" t="n"/>
-      <c r="P115" s="2" t="n"/>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q115" s="2" t="n"/>
       <c r="R115" s="2" t="n"/>
       <c r="S115" s="2" t="n"/>
@@ -10580,10 +10860,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M116" s="2" t="n"/>
-      <c r="N116" s="2" t="n"/>
-      <c r="O116" s="2" t="n"/>
-      <c r="P116" s="2" t="n"/>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q116" s="2" t="n"/>
       <c r="R116" s="2" t="n"/>
       <c r="S116" s="2" t="n"/>
@@ -10672,10 +10966,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M117" s="2" t="n"/>
-      <c r="N117" s="2" t="n"/>
-      <c r="O117" s="2" t="n"/>
-      <c r="P117" s="2" t="n"/>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q117" s="2" t="n"/>
       <c r="R117" s="2" t="n"/>
       <c r="S117" s="2" t="n"/>
@@ -10764,10 +11072,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M118" s="2" t="n"/>
-      <c r="N118" s="2" t="n"/>
-      <c r="O118" s="2" t="n"/>
-      <c r="P118" s="2" t="n"/>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q118" s="2" t="n"/>
       <c r="R118" s="2" t="n"/>
       <c r="S118" s="2" t="n"/>
@@ -10856,10 +11178,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M119" s="2" t="n"/>
-      <c r="N119" s="2" t="n"/>
-      <c r="O119" s="2" t="n"/>
-      <c r="P119" s="2" t="n"/>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q119" s="2" t="n"/>
       <c r="R119" s="2" t="n"/>
       <c r="S119" s="2" t="n"/>
@@ -10948,10 +11284,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M120" s="2" t="n"/>
-      <c r="N120" s="2" t="n"/>
-      <c r="O120" s="2" t="n"/>
-      <c r="P120" s="2" t="n"/>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q120" s="2" t="n"/>
       <c r="R120" s="2" t="n"/>
       <c r="S120" s="2" t="n"/>
@@ -11040,10 +11390,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M121" s="2" t="n"/>
-      <c r="N121" s="2" t="n"/>
-      <c r="O121" s="2" t="n"/>
-      <c r="P121" s="2" t="n"/>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q121" s="2" t="n"/>
       <c r="R121" s="2" t="n"/>
       <c r="S121" s="2" t="n"/>
@@ -11132,10 +11496,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M122" s="2" t="n"/>
-      <c r="N122" s="2" t="n"/>
-      <c r="O122" s="2" t="n"/>
-      <c r="P122" s="2" t="n"/>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q122" s="2" t="n"/>
       <c r="R122" s="2" t="n"/>
       <c r="S122" s="2" t="n"/>
@@ -11224,10 +11602,24 @@
           <t>PyongyangNorth Korea</t>
         </is>
       </c>
-      <c r="M123" s="2" t="n"/>
-      <c r="N123" s="2" t="n"/>
-      <c r="O123" s="2" t="n"/>
-      <c r="P123" s="2" t="n"/>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>KP-01</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>평양시</t>
+        </is>
+      </c>
       <c r="Q123" s="2" t="n"/>
       <c r="R123" s="2" t="n"/>
       <c r="S123" s="2" t="n"/>
